--- a/backend/archives/2026-05/HHG-May-2026.xlsx
+++ b/backend/archives/2026-05/HHG-May-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>Field</t>
   </si>
@@ -99,6 +99,15 @@
   </si>
   <si>
     <t>18/5/2026</t>
+  </si>
+  <si>
+    <t>HHG260500004</t>
+  </si>
+  <si>
+    <t>25/5/2026</t>
+  </si>
+  <si>
+    <t>HHG260500005</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -562,7 +571,7 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -570,7 +579,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>22364</v>
+        <v>32244</v>
       </c>
     </row>
   </sheetData>
@@ -581,7 +590,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -709,33 +718,91 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="3">
-        <v>22364</v>
-      </c>
-      <c r="D5" s="3">
-        <v>22134</v>
-      </c>
-      <c r="E5" s="3">
-        <v>14</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>-245</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="C5">
+        <v>4658</v>
+      </c>
+      <c r="D5">
+        <v>4525</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>-133</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
         <v>30</v>
+      </c>
+      <c r="C6">
+        <v>5222</v>
+      </c>
+      <c r="D6">
+        <v>9848</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>4624</v>
+      </c>
+      <c r="I6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="3">
+        <v>32244</v>
+      </c>
+      <c r="D7" s="3">
+        <v>36507</v>
+      </c>
+      <c r="E7" s="3">
+        <v>18</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2</v>
+      </c>
+      <c r="H7" s="3">
+        <v>4246</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
